--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/octet_spark.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Weapons/octet_spark.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity Projects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Weapons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ABA1E4-35C0-4806-BF25-4F558CF7CF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E62E9-E603-4299-8758-761B99AD0D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31215" yWindow="1875" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2683" yWindow="3797" windowWidth="24694" windowHeight="14597" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes_base" sheetId="1" r:id="rId1"/>
@@ -404,13 +404,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="11" width="12.625" customWidth="1"/>
+    <col min="1" max="2" width="24.640625" customWidth="1"/>
+    <col min="3" max="11" width="12.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +419,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -431,7 +431,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -443,7 +443,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -455,7 +455,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -463,7 +463,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -471,18 +471,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -497,14 +497,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CE5BFE-EF2D-4BBF-853C-AFB047A960B0}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="4" width="24.625" customWidth="1"/>
-    <col min="5" max="5" width="48.625" customWidth="1"/>
-    <col min="6" max="11" width="12.625" customWidth="1"/>
+    <col min="1" max="4" width="24.640625" customWidth="1"/>
+    <col min="5" max="5" width="48.640625" customWidth="1"/>
+    <col min="6" max="11" width="12.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -539,7 +539,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -557,18 +557,18 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
